--- a/shucle_report/충북혁신도시/20260413_20260419/report_충북혁신도시_20260413_20260419.xlsx
+++ b/shucle_report/충북혁신도시/20260413_20260419/report_충북혁신도시_20260413_20260419.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.04.13 ~ 04.19 | 비교기간: 2026.04.06 ~ 04.12 | 생성: 2026-04-20 11:27 | 차트: 117개</t>
+          <t>분석기간: 2026.04.13 ~ 04.19 | 비교기간: 2026.04.06 ~ 04.12 | 생성: 2026-04-20 12:36 | 차트: 129개</t>
         </is>
       </c>
     </row>
@@ -587,22 +587,22 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>130건</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5.9건</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>유지</t>
         </is>
       </c>
     </row>
@@ -624,22 +624,22 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>107건</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2.7건</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>유지</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>130명</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1.6명</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>유지</t>
         </is>
       </c>
     </row>
@@ -1222,22 +1222,22 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -1309,28 +1309,28 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>• 가호출 성공률 상승: 63.7% → 78.8%, 가호출 시도 일평균 764건</t>
+          <t>• 이동완료율 80.9% → 82.4% (+1.6%p): 호출 130건 중 107건 완료 (호출취소 140건, 배차실패 7건)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>• 대기시간 안정: 14.3분 → 13.9분 (-2.8%) — 큰 변동 없음</t>
+          <t>• 가호출 성공률 상승: 63.7% → 78.8%, 가호출 시도 일평균 764건</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>• 성장 현황: DAU 160명, 신규회원 일평균 4.9명, 누적회원 9062명</t>
+          <t>• 호출당 평균 탑승객 1.2명: 1인 이용 위주</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>• 공급 현황: 운행차량 2.0대, 대당 운행시간 8.9시간</t>
+          <t>• 수요 현황: 일평균 호출 130건(-4.3%), 이동완료 107건, 탑승객 130명</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1370,7 +1370,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>▼ 대당 탑승객 수(일평균) (-0.1%)</t>
+          <t>▼ 실시간 호출 건수(일평균) (-4.3%)</t>
         </is>
       </c>
     </row>
@@ -1414,819 +1414,886 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(일평균)</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(평일)</t>
+          <t>가호출 수(일평균)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>851</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>764</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-86.6</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>평일 47.8명 안정</t>
+          <t>가호출 10% 감소</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(일평균)</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(주말)</t>
+          <t>배차실패 건수(일평균)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>+1.4</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>+7.2%</t>
+          <t>-41.7%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>주말 20.3명 (7% 증가)</t>
+          <t>배차실패 건수 42% 감소</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(일평균)</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>동승 인원 분포(일평균)</t>
+          <t>호출취소 건수(일평균)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>호출취소 건수 13% 감소</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(일평균)</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수(일평균)</t>
+          <t>운행차량 대수</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>2대 유지, 증차 여지 없음</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>대당 탑승객 수(일평균)</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>운행차량 대수</t>
+          <t>전화 호출 비율</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.0%p</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>변동 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>앱 호출 비율</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%p</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
           <t>+0.0%</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>2대 유지, 증차 여지 없음</t>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>앱 비중 유지</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>▼ 평균 대기시간 (-2.8%)</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>현장 호출 비율</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%p</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>세부지표</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>비교기간</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>분석기간</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>변동값</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>변동률</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>포인트</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>이동완료 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>-2.5%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
           <t>평균 대기시간</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>평균 대기시간(평일)</t>
-        </is>
-      </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>평일 10.6분 안정</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>평균 대기시간</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>평균 대기시간(주말)</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>+2.9%</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>주말 3.3분 안정</t>
+          <t>13.9분 안정</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>평균 대기시간</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>상위 10% 대기시간</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>-6.2%</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>상위10% 27분, 장시간 대기</t>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>▼ 이동완료 호출 건수(일평균) (-2.5%)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>평균 대기시간</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>장시간 대기(30분+) 비율</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>9.0%</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>7.1%</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>-1.9%p</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>-21.2%</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>30분+ 비율 7%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>평균 대기시간</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>운행차량 대수</t>
+          <t>미탑승 건수(일평균)</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>+0.3</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+20.0%</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2대 유지, 증차 여지 없음</t>
+          <t>미탑승 건수 20% 증가</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>평균 대기시간</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수(일평균)</t>
+          <t>호출취소 건수(일평균)</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>▼ 평균 우회비율 (-1.1%)</t>
+          <t>호출취소 건수 13% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>이동완료 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>배차실패 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>-41.7%</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>배차실패 건수 42% 감소</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>▼ 총 탑승객 수(일평균) (-1.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>평균 우회비율</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>상위 10% 우회비율</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>1.8배 안정</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>평균 우회비율</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>평균 이동시간</t>
+          <t>동승 인원 분포(일평균)</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>6.3분 안정</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>평균 우회비율</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>동승 인원 분포(일평균)</t>
+          <t>고령자(60+) 호출 비율</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2.6%p</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+139.9%</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>분석기간 데이터 없음</t>
+          <t>고령자(60+) 2→4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>총 탑승객 수(일평균)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>성인(20~50대) 호출 비율</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>63.8%</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>61.2%</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>-2.7%p</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>-4.2%</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>성인(20~50대) 비중 유지</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>▼ 평균 이동시간 (-0.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>총 탑승객 수(일평균)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>어린이/청소년 호출 비율</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>34.4%</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>+0.1%p</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>+0.3%</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>어린이/청소년 비중 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>▼ 대당 탑승객 수(일평균) (-0.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>평균 이동시간</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>피크 시간대 이동시간</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>분석기간 데이터 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>평균 이동시간</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>비피크 시간대 이동시간</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>분석기간 데이터 없음</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>평균 이동시간</t>
+          <t>대당 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>평균 우회비율</t>
+          <t>대당 탑승객 수(평일)</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>1.2배 안정</t>
+          <t>평일 47.8명 안정</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>대당 탑승객 수(일평균)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>대당 탑승객 수(주말)</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>+1.4</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>주말 20.3명 (7% 증가)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>─ 운행차량 대수 (+0.0%)</t>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>대당 탑승객 수(일평균)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>동승 인원 분포(일평균)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>-1.2%</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>세부지표</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>비교기간</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>분석기간</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>변동값</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>변동률</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>포인트</t>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>대당 탑승객 수(일평균)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>-5.9</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>-4.3%</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
+          <t>대당 탑승객 수(일평균)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>운행차량 대수</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>일별 운행 차량 수</t>
-        </is>
-      </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -2249,553 +2316,553 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>0% 감소</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>운행차량 대수</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>근무 이행률</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>1.0시간 유지</t>
+          <t>2대 유지, 증차 여지 없음</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>운행차량 대수</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>배차실패 건수(일평균)</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>분석기간 데이터 없음</t>
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>▼ 평균 대기시간 (-2.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>▼ 대당 운행시간(일평균) (-0.6%)</t>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>평균 대기시간</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>평균 대기시간(평일)</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>-4.4%</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>평일 10.6분 안정</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>세부지표</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>비교기간</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>분석기간</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>변동값</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>변동률</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>포인트</t>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>평균 대기시간</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>평균 대기시간(주말)</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>+2.9%</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>주말 3.3분 안정</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>대당 운행시간(일평균)</t>
+          <t>평균 대기시간</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>차량별 운행 시간</t>
+          <t>상위 10% 대기시간</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>상위10% 27분, 장시간 대기</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>대당 운행시간(일평균)</t>
+          <t>평균 대기시간</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>평균 근무시간</t>
+          <t>장시간 대기(30분+) 비율</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>-1.9%p</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>12.3시간 유지</t>
+          <t>30분+ 비율 7%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>대당 운행시간(일평균)</t>
+          <t>평균 대기시간</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>차량 대당 탑승객</t>
+          <t>운행차량 대수</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
+          <t>2대 유지, 증차 여지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>평균 대기시간</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>실시간 호출 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>-5.9</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>-4.3%</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
           <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>▲ 가호출 성공률 (+23.7%)</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>▼ 평균 우회비율 (-1.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>가호출 성공률</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>가호출 성공률(평일)</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>40.1%</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>54.0%</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>+13.8%p</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>+34.4%</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>평일 54% (34% 증가)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공률</t>
+          <t>평균 우회비율</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공률(주말)</t>
+          <t>상위 10% 우회비율</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>+1.3%p</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>+5.4%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>주말 25% (5% 증가)</t>
+          <t>1.8배 안정</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공률</t>
+          <t>평균 우회비율</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대 가호출 성공률</t>
+          <t>평균 이동시간</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>6.3분 안정</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공률</t>
+          <t>평균 우회비율</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공/실패 회원(일평균)</t>
+          <t>동승 인원 분포(일평균)</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>-17.4</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>214.6→197.1명 감소</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>가호출 성공률</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>운행차량 대수</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>+0.0</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>2대 유지, 증차 여지 없음</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>가호출 성공률</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>가호출 수(일평균)</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-86.6</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>-10.2%</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>가호출 10% 감소</t>
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>▼ 평균 이동시간 (-0.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>▲ 평균 경로이탈비중 (+2.7%)</t>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>평균 이동시간</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>피크 시간대(16~18시) 이동시간</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>+6.2%</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>6.0→6.4분 증가</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>세부지표</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>비교기간</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>분석기간</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>변동값</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>변동률</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>포인트</t>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>평균 이동시간</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>비피크 시간대(8~10시) 이동시간</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>+1.6%</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>6.4분 안정</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>평균 경로이탈비중</t>
+          <t>평균 이동시간</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2829,403 +2896,1063 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>평균 경로이탈비중</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>평균 이동시간</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>6.3분 안정</t>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>─ 운행차량 대수 (+0.0%)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>▼ DAU (일간 활성 회원) (-6.5%)</t>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>세부지표</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>비교기간</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>분석기간</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>변동값</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>변동률</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>포인트</t>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>일별 운행 차량 수</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>+0.0</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>0% 감소</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>DAU (일간 활성 회원)</t>
+          <t>운행차량 대수</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>WAU (주간 활성 회원)</t>
+          <t>근무 이행률</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>85.9명 안정</t>
+          <t>1.0시간 유지</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>배차실패 건수(일평균)</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>-41.7%</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>배차실패 건수 42% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>▼ 대당 운행시간(일평균) (-0.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>대당 운행시간(일평균)</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>차량별 운행 시간</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>안정 유지, 영향 제한적</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>대당 운행시간(일평균)</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>평균 근무시간</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>12.3시간 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>대당 운행시간(일평균)</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>차량 대당 탑승객</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>68.2</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>안정 유지, 영향 제한적</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>▲ 가호출 성공률 (+23.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률(평일)</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>40.1%</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>54.0%</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>+13.8%p</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>+34.4%</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>평일 54% (34% 증가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률(주말)</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>24.8%</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>+1.3%p</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>+5.4%</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>주말 25% (5% 증가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>피크 시간대 가호출 성공률</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>데이터 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공/실패 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>-17.4</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>-8.1%</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>214.6→197.1명 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>+0.0</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>2대 유지, 증차 여지 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>가호출 성공률</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>가호출 수(일평균)</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>-86.6</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>-10.2%</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>가호출 10% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>▲ 평균 경로이탈비중 (+2.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>평균 경로이탈비중</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>평균 우회비율</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>1.2배 안정</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>평균 경로이탈비중</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>평균 이동시간</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>6.3분 안정</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>▼ DAU (일간 활성 회원) (-6.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
           <t>DAU (일간 활성 회원)</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>WAU (주간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>85.9</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>-1.9</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>-2.1%</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>85.9명 안정</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>DAU (일간 활성 회원)</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>신규 지역 회원(일평균)</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>+0.1</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>+3.0%</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G86" s="6" t="inlineStr">
         <is>
           <t>신규 4.9명/일 (3% 증가)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>DAU (일간 활성 회원)</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>활성 회원 평균연령</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>29.9</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>30.1</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>+0.2</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>+0.6%</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G87" s="6" t="inlineStr">
         <is>
           <t>평균 30세 (1% 증가)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>DAU (일간 활성 회원)</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>가호출 성공률</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>63.7%</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>78.8%</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>+15.1%p</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>+23.7%</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>소폭 역방향 증가</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>DAU (일간 활성 회원)</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>평균 대기시간</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>13.9</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>-0.4</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>-2.8%</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>13.9분 안정</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>▲ 신규 지역 회원(일평균) (+3.0%)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>신규 지역 회원(일평균)</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>누적 지역 회원(일평균)</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>9,016</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>9,048</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>+32.6</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>+0.4%</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>누적 9048명 (0% 증가)</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>신규 지역 회원(일평균)</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>가호출 순 회원(일평균)</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>-11.1</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>-6.5%</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>171.4→160.3명 감소</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A58:G58"/>
+  <mergeCells count="14">
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="A91:G91"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
